--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88627121</v>
+        <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>80467</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518344</v>
+        <v>518336</v>
       </c>
       <c r="R2" t="n">
-        <v>6639802</v>
+        <v>6639841</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +770,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,16 +790,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88627121</t>
+          <t>https://artportalen.se/Sighting/136940449</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75195514</v>
+        <v>88627121</v>
       </c>
       <c r="B3" t="n">
-        <v>80392</v>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +807,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malingsbo-Kloten, Dlr</t>
+          <t>Kloten, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518345</v>
+        <v>518344</v>
       </c>
       <c r="R3" t="n">
-        <v>6639819</v>
+        <v>6639802</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,31 +890,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75195514</t>
+          <t>https://artportalen.se/Sighting/88627121</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88627120</v>
+        <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>80392</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -930,21 +940,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kloten, Dlr</t>
+          <t>Kloten - Gruvens, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518344</v>
+        <v>518353</v>
       </c>
       <c r="R4" t="n">
-        <v>6639742</v>
+        <v>6639841</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,6 +1000,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1002,7 +1020,804 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136940458</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136940451</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518313</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6639874</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940451</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136940450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518353</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6639830</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940450</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136940453</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>518347</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6639819</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940453</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136940447</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>518375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6639808</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940447</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>75195514</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Malingsbo-Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>518345</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6639819</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195514</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88627120</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kloten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>518344</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6639742</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88627120</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136940448</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kloten - Gruvens, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518331</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6639752</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136940448</t>
         </is>
       </c>
     </row>
@@ -1011,6 +1826,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136940451</v>
       </c>
       <c r="B5" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136940451</v>
       </c>
       <c r="B5" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -942,11 +942,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1059,11 +1055,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kloten - Gruvens, Dlr</t>
@@ -1175,11 +1167,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kloten - Gruvens, Dlr</t>
@@ -1291,11 +1279,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kloten - Gruvens, Dlr</t>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136940451</v>
       </c>
       <c r="B5" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136940451</v>
       </c>
       <c r="B5" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104968</v>
+        <v>104970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2447-2026 artfynd.xlsx
+++ b/artfynd/S 2447-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940449</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136940458</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136940451</v>
       </c>
       <c r="B5" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136940450</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136940453</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136940447</v>
       </c>
       <c r="B8" t="n">
-        <v>104970</v>
+        <v>104974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136940448</v>
       </c>
       <c r="B11" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
